--- a/nightwatch/ACTVN_TestCases.xlsx
+++ b/nightwatch/ACTVN_TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vien1\Downloads\OceanTech\School\kiemThuNhung\nightwatch-git\nightwatch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724ADED5-F176-4F83-ACCA-C2F4E5C27246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70F0B2A-11BF-4141-961E-F4F4D0306847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>ID</t>
   </si>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>TC02</t>
-  </si>
-  <si>
-    <t>Kiểm tra hiển thị trang Liên hệ</t>
   </si>
   <si>
     <t>Đảm bảo trang Liên hệ có thông tin liên lạc</t>
@@ -122,9 +119,13 @@
     <t>cập nhật thành công</t>
   </si>
   <si>
+    <t>Xuất hiện alert với nội dung là "Bạn cập nhật thành công", sau đó nhấn OK</t>
+  </si>
+  <si>
     <t>Mở trình duyệt
 Truy cập trang "http://thuvienso.actvn.edu.vn"
 Bấm vào "Thiết lập tài khoản"
+Tải tệp "test.jpg" lên tại ô có id "txtFile"
 Chọn thẻ có id là "txtLastname"
 Gõ "Trần Văn"
 Chọn thẻ có id là "txtFirstname"
@@ -136,18 +137,32 @@
 Bấm vào "Cập nhật"</t>
   </si>
   <si>
-    <t>Xuất hiện alert với nội dung là "Bạn cập nhật thành công", sau đó nhấn OK</t>
+    <t>kiểm tra chức năng cập nhật thông tin với các kết quả đúng</t>
+  </si>
+  <si>
+    <t>Kiểm tra đăng nhập</t>
+  </si>
+  <si>
+    <t>Kiểm tra cập nhật thông tin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -246,28 +261,28 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -554,26 +569,26 @@
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
+      <c r="E2" s="5" t="s">
+        <v>16</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>15</v>
+      <c r="H2" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -596,30 +611,30 @@
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
     </row>
-    <row r="3" spans="1:28" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" ht="202.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>12</v>
+      <c r="B3" s="8" t="s">
+        <v>23</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="F3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>21</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>

--- a/nightwatch/ACTVN_TestCases.xlsx
+++ b/nightwatch/ACTVN_TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vien1\Downloads\OceanTech\School\kiemThuNhung\nightwatch-git\nightwatch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70F0B2A-11BF-4141-961E-F4F4D0306847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FFFCD21-6162-421C-8B5D-1126FEFC55CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="152">
   <si>
     <t>ID</t>
   </si>
@@ -63,57 +63,7 @@
     <t>TC02</t>
   </si>
   <si>
-    <t>Đảm bảo trang Liên hệ có thông tin liên lạc</t>
-  </si>
-  <si>
     <t>Click menu/mục tương ứng</t>
-  </si>
-  <si>
-    <t>Kiểm tra thấy "Thiết lập tài khoản"</t>
-  </si>
-  <si>
-    <r>
-      <t>Mở trình duyệt
-Truy cập trang "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://thuvienso.actvn.edu.vn"
-Chọn thẻ có id là "txtLoginUsername"
-Gõ "CT020126"
-Chọn thẻ có id là "txtLoginPassword"
-Gõ "CT020126"
-Bấm vào "Đăng nhập"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Mở trình duyệt
-2. Truy cập trang </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://actvn.edu.vn
-3. Hover vào mục 'Giới thiệu' trên navbar
-4. Click vào mục 'Liên hệ'</t>
-    </r>
-  </si>
-  <si>
-    <t>đăng nhập thành công</t>
   </si>
   <si>
     <t>cập nhật thành công</t>
@@ -140,21 +90,705 @@
     <t>kiểm tra chức năng cập nhật thông tin với các kết quả đúng</t>
   </si>
   <si>
-    <t>Kiểm tra đăng nhập</t>
+    <t>TC_ẢNH_02</t>
   </si>
   <si>
-    <t>Kiểm tra cập nhật thông tin</t>
+    <t>Upload ảnh - Không chọn</t>
+  </si>
+  <si>
+    <t>Kiểm tra khi không upload ảnh</t>
+  </si>
+  <si>
+    <t>Không upload ảnh</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <t>thông báo lỗi thiếu ảnh</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "Trần Văn"
+Chọn thẻ có id là "txtFirstname"
+Gõ "Huy"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>TestCase đúng làm chuẩn để các testcase khác tham chiếu thay đổi dữ liệu</t>
+  </si>
+  <si>
+    <t>TC_HO_01</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập họ có dấu tiếng Việt</t>
+  </si>
+  <si>
+    <t>Kiểm tra hệ thống xử lý đúng họ có dấu tiếng Việt</t>
+  </si>
+  <si>
+    <t>Gõ "Nguyễn Văn" vào ô họ</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "Nguyễn Văn"
+Chọn thẻ có id là "txtFirstname"
+Gõ "Huy"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>TC_HO_02</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập họ không dấu</t>
+  </si>
+  <si>
+    <t>Kiểm tra hệ thống xử lý họ không dấu tiếng Việt</t>
+  </si>
+  <si>
+    <t>Gõ "Nguyen Van" vào ô họ</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "Nguyen Van"
+Chọn thẻ có id là "txtFirstname"
+Gõ "Huy"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>TC_HO_03</t>
+  </si>
+  <si>
+    <t>Kiểm tra bỏ trống trường họ</t>
+  </si>
+  <si>
+    <t>Kiểm tra cảnh báo khi không nhập họ</t>
+  </si>
+  <si>
+    <t>Bỏ trống ô họ</t>
+  </si>
+  <si>
+    <t>hiện thông báo lỗi trường bắt buộc</t>
+  </si>
+  <si>
+    <t>Xuất hiện alert với nội dung là "Vui lòng nhập họ", sau đó nhấn OK</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ ""
+Chọn thẻ có id là "txtFirstname"
+Gõ "Huy"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>TC_HO_04</t>
+  </si>
+  <si>
+    <t>Kiểm tra trường họ chỉ có khoảng trắng</t>
+  </si>
+  <si>
+    <t>Kiểm tra cảnh báo khi trường họ chỉ chứa khoảng trắng</t>
+  </si>
+  <si>
+    <t>Gõ " " vào ô họ</t>
+  </si>
+  <si>
+    <t>hiện thông báo lỗi trường không hợp lệ</t>
+  </si>
+  <si>
+    <t>Xuất hiện alert với nội dung là "Họ không hợp lệ", sau đó nhấn OK</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ " "
+Chọn thẻ có id là "txtFirstname"
+Gõ "Huy"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>TC_HO_06</t>
+  </si>
+  <si>
+    <t>Họ chứa số</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập họ có chứa số</t>
+  </si>
+  <si>
+    <t>Gõ "Trần123"</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi "Họ không được chứa số"</t>
+  </si>
+  <si>
+    <t>Xuất hiện alert với nội dung là "Họ không được chứa số", sau đó nhấn OK</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "Trần123"
+Chọn thẻ có id là "txtFirstname"
+Gõ "Huy"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>TC_HO_07</t>
+  </si>
+  <si>
+    <t>Họ chứa ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập họ có ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>Gõ "Trần@!"</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi "Họ không được chứa ký tự đặc biệt"</t>
+  </si>
+  <si>
+    <t>Xuất hiện alert với nội dung là "Họ không được chứa ký tự đặc biệt", sau đó nhấn OK</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "Trần@!"
+Chọn thẻ có id là "txtFirstname"
+Gõ "Huy"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>TC_HO_08</t>
+  </si>
+  <si>
+    <t>Họ vượt quá 255 ký tự</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập họ dài hơn 255 ký tự</t>
+  </si>
+  <si>
+    <t>Gõ chuỗi 256 ký tự "A..."</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi "Họ không được vượt quá 255 ký tự"</t>
+  </si>
+  <si>
+    <t>Xuất hiện alert với nội dung là "Họ không được vượt quá 255 ký tự", sau đó nhấn OK</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA"
+Chọn thẻ có id là "txtFirstname"
+Gõ "Huy"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>TC_HO_09</t>
+  </si>
+  <si>
+    <t>Họ chứa emoji</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập họ có chứa emoji</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gõ "Trần </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>😊</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi "Họ không được chứa ký tự không hợp lệ"</t>
+  </si>
+  <si>
+    <t>Xuất hiện alert với nội dung là "Họ không được chứa ký tự không hợp lệ", sau đó nhấn OK</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "Trần 😊"
+Chọn thẻ có id là "txtFirstname"
+Gõ "Huy"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>TC_HO_10</t>
+  </si>
+  <si>
+    <t>Họ chứa chữ nước ngoài</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập họ có chữ tiếng nước ngoài</t>
+  </si>
+  <si>
+    <t>Gõ "Nguyễn Hans"</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi "Họ không hợp lệ"</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "陈氏"
+Chọn thẻ có id là "txtFirstname"
+Gõ "Huy"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>Họ có khoảng trắng đầu/cuối</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập họ bắt đầu và kết thúc bằng khoảng trắng</t>
+  </si>
+  <si>
+    <t>Gõ " Nguyễn "</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ " Nguyễn "
+Chọn thẻ có id là "txtFirstname"
+Gõ "Huy"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>TC_HO_05</t>
+  </si>
+  <si>
+    <t>TC_TEN_01</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập tên có dấu tiếng Việt</t>
+  </si>
+  <si>
+    <t>Kiểm tra hệ thống xử lý đúng tên có dấu tiếng Việt</t>
+  </si>
+  <si>
+    <t>Gõ "Nguyễn Văn" vào ô tên</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "Trần Văn"
+Chọn thẻ có id là "txtFirstname"
+Gõ "Hà"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>TC_TEN_02</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập tên không dấu</t>
+  </si>
+  <si>
+    <t>Kiểm tra hệ thống xử lý tên không dấu tiếng Việt</t>
+  </si>
+  <si>
+    <t>Gõ "Nguyen Van" vào ô tên</t>
+  </si>
+  <si>
+    <t>TC_TEN_03</t>
+  </si>
+  <si>
+    <t>Kiểm tra bỏ trống trường tên</t>
+  </si>
+  <si>
+    <t>Kiểm tra cảnh báo khi không nhập tên</t>
+  </si>
+  <si>
+    <t>Bỏ trống ô tên</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "Trần Văn"
+Chọn thẻ có id là "txtFirstname"
+Gõ ""
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>Xuất hiện alert với nội dung là "Vui lòng nhập tên", sau đó nhấn OK</t>
+  </si>
+  <si>
+    <t>TC_TEN_04</t>
+  </si>
+  <si>
+    <t>Kiểm tra trường tên chỉ có khoảng trắng</t>
+  </si>
+  <si>
+    <t>Kiểm tra cảnh báo khi trường tên chỉ chứa khoảng trắng</t>
+  </si>
+  <si>
+    <t>Gõ " " vào ô tên</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "Trần Văn"
+Chọn thẻ có id là "txtFirstname"
+Gõ " "
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>Xuất hiện alert với nội dung là "Tên không hợp lệ", sau đó nhấn OK</t>
+  </si>
+  <si>
+    <t>TC_TEN_05</t>
+  </si>
+  <si>
+    <t>Tên chứa số</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập tên có chứa số</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "Trần Văn"
+Chọn thẻ có id là "txtFirstname"
+Gõ "Trần123"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi "Tên không được chứa số"</t>
+  </si>
+  <si>
+    <t>Xuất hiện alert với nội dung là "Tên không được chứa số", sau đó nhấn OK</t>
+  </si>
+  <si>
+    <t>TC_TEN_06</t>
+  </si>
+  <si>
+    <t>Tên chứa ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập tên có ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "Trần Văn"
+Chọn thẻ có id là "txtFirstname"
+Gõ "Trần@!"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi "Tên không được chứa ký tự đặc biệt"</t>
+  </si>
+  <si>
+    <t>Xuất hiện alert với nội dung là "Tên không được chứa ký tự đặc biệt", sau đó nhấn OK</t>
+  </si>
+  <si>
+    <t>TC_TEN_07</t>
+  </si>
+  <si>
+    <t>Tên vượt quá 255 ký tự</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập tên dài hơn 255 ký tự</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "Trần Văn"
+Chọn thẻ có id là "txtFirstname"
+Gõ "AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi "Tên không được vượt quá 255 ký tự"</t>
+  </si>
+  <si>
+    <t>Xuất hiện alert với nội dung là "Tên không được vượt quá 255 ký tự", sau đó nhấn OK</t>
+  </si>
+  <si>
+    <t>TC_TEN_08</t>
+  </si>
+  <si>
+    <t>Tên chứa emoji</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập tên có chứa emoji</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "Trần Văn"
+Chọn thẻ có id là "txtFirstname"
+Gõ "Trần 😊"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi "Tên không được chứa ký tự không hợp lệ"</t>
+  </si>
+  <si>
+    <t>Xuất hiện alert với nội dung là "Tên không được chứa ký tự không hợp lệ", sau đó nhấn OK</t>
+  </si>
+  <si>
+    <t>TC_TEN_09</t>
+  </si>
+  <si>
+    <t>Tên chứa chữ nước ngoài</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập tên có chữ tiếng nước ngoài</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "Trần Văn"
+Chọn thẻ có id là "txtFirstname"
+Gõ "陈氏"
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi "Tên không hợp lệ"</t>
+  </si>
+  <si>
+    <t>TC_TEN_10</t>
+  </si>
+  <si>
+    <t>Tên có khoảng trắng đầu/cuối</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập tên bắt đầu và kết thúc bằng khoảng trắng</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Bấm vào "Thiết lập tài khoản"
+Không upload ảnh
+Chọn thẻ có id là "txtLastname"
+Gõ "Trần Văn"
+Chọn thẻ có id là "txtFirstname"
+Gõ " Nguyễn "
+Chọn "10" từ "ngày" được xổ xuống
+Chọn "5" từ "tháng" được xổ xuống
+Chọn "2003" từ "năm" được xổ xuống
+Chọn radio "Nam"
+Bấm vào "Cập nhật"</t>
+  </si>
+  <si>
+    <t>TC01</t>
+  </si>
+  <si>
+    <t>kiểm tra đăng nhập</t>
+  </si>
+  <si>
+    <t>Đảm bảo trang có thể đăng nhập</t>
+  </si>
+  <si>
+    <t>Tài khoản đăng nhập (CT020126/CT020126)</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Chọn thẻ có id là "txtLoginUsername"
+Gõ "CT020126"
+Chọn thẻ có id là "txtLoginPassword"
+Gõ "CT020126"
+Bấm vào "Đăng nhập"</t>
+  </si>
+  <si>
+    <t>Kiểm tra thấy "Thiết lập tài khoản"</t>
+  </si>
+  <si>
+    <t>Xuất hiện alert với nội dung là "Họ không được chứa khoảng trắng", sau đó nhấn OK</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi "Họ không được chứa khoảng trắng"</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi "Tên không được chứa khoảng trắng"</t>
+  </si>
+  <si>
+    <t>Xuất hiện alert với nội dung là "Tên không được chứa khoảng trắng", sau đó nhấn OK</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -193,6 +827,28 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -202,7 +858,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -255,34 +911,88 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -500,7 +1210,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB970"/>
+  <dimension ref="A1:AB948"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -565,76 +1275,76 @@
       <c r="AA1" s="2"/>
       <c r="AB1" s="2"/>
     </row>
-    <row r="2" spans="1:28" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:28" s="18" customFormat="1" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+    </row>
+    <row r="3" spans="1:28" ht="202.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>22</v>
+      <c r="B3" s="11" t="s">
+        <v>24</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-    </row>
-    <row r="3" spans="1:28" ht="202.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -657,48 +1367,84 @@
       <c r="AA3" s="4"/>
       <c r="AB3" s="4"/>
     </row>
-    <row r="4" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-    </row>
-    <row r="5" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+    <row r="4" spans="1:28" s="9" customFormat="1" ht="202.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
+      <c r="Z4" s="8"/>
+      <c r="AA4" s="8"/>
+      <c r="AB4" s="8"/>
+    </row>
+    <row r="5" spans="1:28" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -717,18 +1463,34 @@
       <c r="AA5" s="2"/>
       <c r="AB5" s="2"/>
     </row>
-    <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+    <row r="6" spans="1:28" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -748,15 +1510,31 @@
       <c r="AB6" s="2"/>
     </row>
     <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="A7" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="11"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -778,15 +1556,31 @@
       <c r="AB7" s="2"/>
     </row>
     <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="A8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="11"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -808,15 +1602,31 @@
       <c r="AB8" s="2"/>
     </row>
     <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="A9" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="11"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -838,16 +1648,32 @@
       <c r="AB9" s="2"/>
     </row>
     <row r="10" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="A10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -868,16 +1694,32 @@
       <c r="AB10" s="2"/>
     </row>
     <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
+      <c r="A11" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
@@ -897,17 +1739,33 @@
       <c r="AA11" s="2"/>
       <c r="AB11" s="2"/>
     </row>
-    <row r="12" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+    <row r="12" spans="1:28" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -928,16 +1786,32 @@
       <c r="AB12" s="2"/>
     </row>
     <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
+      <c r="A13" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -958,16 +1832,32 @@
       <c r="AB13" s="2"/>
     </row>
     <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
+      <c r="A14" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -987,317 +1877,473 @@
       <c r="AA14" s="2"/>
       <c r="AB14" s="2"/>
     </row>
-    <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
-      <c r="Y15" s="2"/>
-      <c r="Z15" s="2"/>
-      <c r="AA15" s="2"/>
-      <c r="AB15" s="2"/>
-    </row>
-    <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
-      <c r="Z16" s="2"/>
-      <c r="AA16" s="2"/>
-      <c r="AB16" s="2"/>
-    </row>
-    <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
-      <c r="Z17" s="2"/>
-      <c r="AA17" s="2"/>
-      <c r="AB17" s="2"/>
-    </row>
-    <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2"/>
-      <c r="Y18" s="2"/>
-      <c r="Z18" s="2"/>
-      <c r="AA18" s="2"/>
-      <c r="AB18" s="2"/>
-    </row>
-    <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="2"/>
-      <c r="AA19" s="2"/>
-      <c r="AB19" s="2"/>
-    </row>
-    <row r="20" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="2"/>
-      <c r="AA20" s="2"/>
-      <c r="AB20" s="2"/>
-    </row>
-    <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
-      <c r="AA21" s="2"/>
-      <c r="AB21" s="2"/>
-    </row>
-    <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2"/>
-      <c r="Z22" s="2"/>
-      <c r="AA22" s="2"/>
-      <c r="AB22" s="2"/>
-    </row>
-    <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="2"/>
-      <c r="Z23" s="2"/>
-      <c r="AA23" s="2"/>
-      <c r="AB23" s="2"/>
-    </row>
-    <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-      <c r="Z24" s="2"/>
-      <c r="AA24" s="2"/>
-      <c r="AB24" s="2"/>
+    <row r="15" spans="1:28" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="11"/>
+      <c r="AA15" s="11"/>
+      <c r="AB15" s="11"/>
+    </row>
+    <row r="16" spans="1:28" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
+      <c r="AA16" s="11"/>
+      <c r="AB16" s="11"/>
+    </row>
+    <row r="17" spans="1:28" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="11"/>
+      <c r="W17" s="11"/>
+      <c r="X17" s="11"/>
+      <c r="Y17" s="11"/>
+      <c r="Z17" s="11"/>
+      <c r="AA17" s="11"/>
+      <c r="AB17" s="11"/>
+    </row>
+    <row r="18" spans="1:28" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
+      <c r="V18" s="11"/>
+      <c r="W18" s="11"/>
+      <c r="X18" s="11"/>
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="11"/>
+      <c r="AA18" s="11"/>
+      <c r="AB18" s="11"/>
+    </row>
+    <row r="19" spans="1:28" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
+      <c r="T19" s="11"/>
+      <c r="U19" s="11"/>
+      <c r="V19" s="11"/>
+      <c r="W19" s="11"/>
+      <c r="X19" s="11"/>
+      <c r="Y19" s="11"/>
+      <c r="Z19" s="11"/>
+      <c r="AA19" s="11"/>
+      <c r="AB19" s="11"/>
+    </row>
+    <row r="20" spans="1:28" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+      <c r="T20" s="11"/>
+      <c r="U20" s="11"/>
+      <c r="V20" s="11"/>
+      <c r="W20" s="11"/>
+      <c r="X20" s="11"/>
+      <c r="Y20" s="11"/>
+      <c r="Z20" s="11"/>
+      <c r="AA20" s="11"/>
+      <c r="AB20" s="11"/>
+    </row>
+    <row r="21" spans="1:28" ht="331.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="11"/>
+      <c r="T21" s="11"/>
+      <c r="U21" s="11"/>
+      <c r="V21" s="11"/>
+      <c r="W21" s="11"/>
+      <c r="X21" s="11"/>
+      <c r="Y21" s="11"/>
+      <c r="Z21" s="11"/>
+      <c r="AA21" s="11"/>
+      <c r="AB21" s="11"/>
+    </row>
+    <row r="22" spans="1:28" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="11"/>
+      <c r="Y22" s="11"/>
+      <c r="Z22" s="11"/>
+      <c r="AA22" s="11"/>
+      <c r="AB22" s="11"/>
+    </row>
+    <row r="23" spans="1:28" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
+      <c r="T23" s="11"/>
+      <c r="U23" s="11"/>
+      <c r="V23" s="11"/>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+      <c r="Z23" s="11"/>
+      <c r="AA23" s="11"/>
+      <c r="AB23" s="11"/>
+    </row>
+    <row r="24" spans="1:28" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="11"/>
+      <c r="V24" s="11"/>
+      <c r="W24" s="11"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="11"/>
+      <c r="Z24" s="11"/>
+      <c r="AA24" s="11"/>
+      <c r="AB24" s="11"/>
     </row>
     <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -1318,16 +2364,16 @@
       <c r="AB25" s="2"/>
     </row>
     <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -1348,16 +2394,16 @@
       <c r="AB26" s="2"/>
     </row>
     <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -29007,668 +30053,12 @@
       <c r="AA948" s="2"/>
       <c r="AB948" s="2"/>
     </row>
-    <row r="949" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A949" s="2"/>
-      <c r="B949" s="2"/>
-      <c r="C949" s="2"/>
-      <c r="D949" s="2"/>
-      <c r="E949" s="2"/>
-      <c r="F949" s="2"/>
-      <c r="G949" s="2"/>
-      <c r="H949" s="2"/>
-      <c r="I949" s="2"/>
-      <c r="J949" s="2"/>
-      <c r="K949" s="2"/>
-      <c r="L949" s="2"/>
-      <c r="M949" s="2"/>
-      <c r="N949" s="2"/>
-      <c r="O949" s="2"/>
-      <c r="P949" s="2"/>
-      <c r="Q949" s="2"/>
-      <c r="R949" s="2"/>
-      <c r="S949" s="2"/>
-      <c r="T949" s="2"/>
-      <c r="U949" s="2"/>
-      <c r="V949" s="2"/>
-      <c r="W949" s="2"/>
-      <c r="X949" s="2"/>
-      <c r="Y949" s="2"/>
-      <c r="Z949" s="2"/>
-      <c r="AA949" s="2"/>
-      <c r="AB949" s="2"/>
-    </row>
-    <row r="950" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A950" s="2"/>
-      <c r="B950" s="2"/>
-      <c r="C950" s="2"/>
-      <c r="D950" s="2"/>
-      <c r="E950" s="2"/>
-      <c r="F950" s="2"/>
-      <c r="G950" s="2"/>
-      <c r="H950" s="2"/>
-      <c r="I950" s="2"/>
-      <c r="J950" s="2"/>
-      <c r="K950" s="2"/>
-      <c r="L950" s="2"/>
-      <c r="M950" s="2"/>
-      <c r="N950" s="2"/>
-      <c r="O950" s="2"/>
-      <c r="P950" s="2"/>
-      <c r="Q950" s="2"/>
-      <c r="R950" s="2"/>
-      <c r="S950" s="2"/>
-      <c r="T950" s="2"/>
-      <c r="U950" s="2"/>
-      <c r="V950" s="2"/>
-      <c r="W950" s="2"/>
-      <c r="X950" s="2"/>
-      <c r="Y950" s="2"/>
-      <c r="Z950" s="2"/>
-      <c r="AA950" s="2"/>
-      <c r="AB950" s="2"/>
-    </row>
-    <row r="951" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A951" s="2"/>
-      <c r="B951" s="2"/>
-      <c r="C951" s="2"/>
-      <c r="D951" s="2"/>
-      <c r="E951" s="2"/>
-      <c r="F951" s="2"/>
-      <c r="G951" s="2"/>
-      <c r="H951" s="2"/>
-      <c r="I951" s="2"/>
-      <c r="J951" s="2"/>
-      <c r="K951" s="2"/>
-      <c r="L951" s="2"/>
-      <c r="M951" s="2"/>
-      <c r="N951" s="2"/>
-      <c r="O951" s="2"/>
-      <c r="P951" s="2"/>
-      <c r="Q951" s="2"/>
-      <c r="R951" s="2"/>
-      <c r="S951" s="2"/>
-      <c r="T951" s="2"/>
-      <c r="U951" s="2"/>
-      <c r="V951" s="2"/>
-      <c r="W951" s="2"/>
-      <c r="X951" s="2"/>
-      <c r="Y951" s="2"/>
-      <c r="Z951" s="2"/>
-      <c r="AA951" s="2"/>
-      <c r="AB951" s="2"/>
-    </row>
-    <row r="952" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A952" s="2"/>
-      <c r="B952" s="2"/>
-      <c r="C952" s="2"/>
-      <c r="D952" s="2"/>
-      <c r="E952" s="2"/>
-      <c r="F952" s="2"/>
-      <c r="G952" s="2"/>
-      <c r="H952" s="2"/>
-      <c r="I952" s="2"/>
-      <c r="J952" s="2"/>
-      <c r="K952" s="2"/>
-      <c r="L952" s="2"/>
-      <c r="M952" s="2"/>
-      <c r="N952" s="2"/>
-      <c r="O952" s="2"/>
-      <c r="P952" s="2"/>
-      <c r="Q952" s="2"/>
-      <c r="R952" s="2"/>
-      <c r="S952" s="2"/>
-      <c r="T952" s="2"/>
-      <c r="U952" s="2"/>
-      <c r="V952" s="2"/>
-      <c r="W952" s="2"/>
-      <c r="X952" s="2"/>
-      <c r="Y952" s="2"/>
-      <c r="Z952" s="2"/>
-      <c r="AA952" s="2"/>
-      <c r="AB952" s="2"/>
-    </row>
-    <row r="953" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A953" s="2"/>
-      <c r="B953" s="2"/>
-      <c r="C953" s="2"/>
-      <c r="D953" s="2"/>
-      <c r="E953" s="2"/>
-      <c r="F953" s="2"/>
-      <c r="G953" s="2"/>
-      <c r="H953" s="2"/>
-      <c r="I953" s="2"/>
-      <c r="J953" s="2"/>
-      <c r="K953" s="2"/>
-      <c r="L953" s="2"/>
-      <c r="M953" s="2"/>
-      <c r="N953" s="2"/>
-      <c r="O953" s="2"/>
-      <c r="P953" s="2"/>
-      <c r="Q953" s="2"/>
-      <c r="R953" s="2"/>
-      <c r="S953" s="2"/>
-      <c r="T953" s="2"/>
-      <c r="U953" s="2"/>
-      <c r="V953" s="2"/>
-      <c r="W953" s="2"/>
-      <c r="X953" s="2"/>
-      <c r="Y953" s="2"/>
-      <c r="Z953" s="2"/>
-      <c r="AA953" s="2"/>
-      <c r="AB953" s="2"/>
-    </row>
-    <row r="954" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A954" s="2"/>
-      <c r="B954" s="2"/>
-      <c r="C954" s="2"/>
-      <c r="D954" s="2"/>
-      <c r="E954" s="2"/>
-      <c r="F954" s="2"/>
-      <c r="G954" s="2"/>
-      <c r="H954" s="2"/>
-      <c r="I954" s="2"/>
-      <c r="J954" s="2"/>
-      <c r="K954" s="2"/>
-      <c r="L954" s="2"/>
-      <c r="M954" s="2"/>
-      <c r="N954" s="2"/>
-      <c r="O954" s="2"/>
-      <c r="P954" s="2"/>
-      <c r="Q954" s="2"/>
-      <c r="R954" s="2"/>
-      <c r="S954" s="2"/>
-      <c r="T954" s="2"/>
-      <c r="U954" s="2"/>
-      <c r="V954" s="2"/>
-      <c r="W954" s="2"/>
-      <c r="X954" s="2"/>
-      <c r="Y954" s="2"/>
-      <c r="Z954" s="2"/>
-      <c r="AA954" s="2"/>
-      <c r="AB954" s="2"/>
-    </row>
-    <row r="955" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A955" s="2"/>
-      <c r="B955" s="2"/>
-      <c r="C955" s="2"/>
-      <c r="D955" s="2"/>
-      <c r="E955" s="2"/>
-      <c r="F955" s="2"/>
-      <c r="G955" s="2"/>
-      <c r="H955" s="2"/>
-      <c r="I955" s="2"/>
-      <c r="J955" s="2"/>
-      <c r="K955" s="2"/>
-      <c r="L955" s="2"/>
-      <c r="M955" s="2"/>
-      <c r="N955" s="2"/>
-      <c r="O955" s="2"/>
-      <c r="P955" s="2"/>
-      <c r="Q955" s="2"/>
-      <c r="R955" s="2"/>
-      <c r="S955" s="2"/>
-      <c r="T955" s="2"/>
-      <c r="U955" s="2"/>
-      <c r="V955" s="2"/>
-      <c r="W955" s="2"/>
-      <c r="X955" s="2"/>
-      <c r="Y955" s="2"/>
-      <c r="Z955" s="2"/>
-      <c r="AA955" s="2"/>
-      <c r="AB955" s="2"/>
-    </row>
-    <row r="956" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A956" s="2"/>
-      <c r="B956" s="2"/>
-      <c r="C956" s="2"/>
-      <c r="D956" s="2"/>
-      <c r="E956" s="2"/>
-      <c r="F956" s="2"/>
-      <c r="G956" s="2"/>
-      <c r="H956" s="2"/>
-      <c r="I956" s="2"/>
-      <c r="J956" s="2"/>
-      <c r="K956" s="2"/>
-      <c r="L956" s="2"/>
-      <c r="M956" s="2"/>
-      <c r="N956" s="2"/>
-      <c r="O956" s="2"/>
-      <c r="P956" s="2"/>
-      <c r="Q956" s="2"/>
-      <c r="R956" s="2"/>
-      <c r="S956" s="2"/>
-      <c r="T956" s="2"/>
-      <c r="U956" s="2"/>
-      <c r="V956" s="2"/>
-      <c r="W956" s="2"/>
-      <c r="X956" s="2"/>
-      <c r="Y956" s="2"/>
-      <c r="Z956" s="2"/>
-      <c r="AA956" s="2"/>
-      <c r="AB956" s="2"/>
-    </row>
-    <row r="957" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A957" s="2"/>
-      <c r="B957" s="2"/>
-      <c r="C957" s="2"/>
-      <c r="D957" s="2"/>
-      <c r="E957" s="2"/>
-      <c r="F957" s="2"/>
-      <c r="G957" s="2"/>
-      <c r="H957" s="2"/>
-      <c r="I957" s="2"/>
-      <c r="J957" s="2"/>
-      <c r="K957" s="2"/>
-      <c r="L957" s="2"/>
-      <c r="M957" s="2"/>
-      <c r="N957" s="2"/>
-      <c r="O957" s="2"/>
-      <c r="P957" s="2"/>
-      <c r="Q957" s="2"/>
-      <c r="R957" s="2"/>
-      <c r="S957" s="2"/>
-      <c r="T957" s="2"/>
-      <c r="U957" s="2"/>
-      <c r="V957" s="2"/>
-      <c r="W957" s="2"/>
-      <c r="X957" s="2"/>
-      <c r="Y957" s="2"/>
-      <c r="Z957" s="2"/>
-      <c r="AA957" s="2"/>
-      <c r="AB957" s="2"/>
-    </row>
-    <row r="958" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A958" s="2"/>
-      <c r="B958" s="2"/>
-      <c r="C958" s="2"/>
-      <c r="D958" s="2"/>
-      <c r="E958" s="2"/>
-      <c r="F958" s="2"/>
-      <c r="G958" s="2"/>
-      <c r="H958" s="2"/>
-      <c r="I958" s="2"/>
-      <c r="J958" s="2"/>
-      <c r="K958" s="2"/>
-      <c r="L958" s="2"/>
-      <c r="M958" s="2"/>
-      <c r="N958" s="2"/>
-      <c r="O958" s="2"/>
-      <c r="P958" s="2"/>
-      <c r="Q958" s="2"/>
-      <c r="R958" s="2"/>
-      <c r="S958" s="2"/>
-      <c r="T958" s="2"/>
-      <c r="U958" s="2"/>
-      <c r="V958" s="2"/>
-      <c r="W958" s="2"/>
-      <c r="X958" s="2"/>
-      <c r="Y958" s="2"/>
-      <c r="Z958" s="2"/>
-      <c r="AA958" s="2"/>
-      <c r="AB958" s="2"/>
-    </row>
-    <row r="959" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A959" s="2"/>
-      <c r="B959" s="2"/>
-      <c r="C959" s="2"/>
-      <c r="D959" s="2"/>
-      <c r="E959" s="2"/>
-      <c r="F959" s="2"/>
-      <c r="G959" s="2"/>
-      <c r="H959" s="2"/>
-      <c r="I959" s="2"/>
-      <c r="J959" s="2"/>
-      <c r="K959" s="2"/>
-      <c r="L959" s="2"/>
-      <c r="M959" s="2"/>
-      <c r="N959" s="2"/>
-      <c r="O959" s="2"/>
-      <c r="P959" s="2"/>
-      <c r="Q959" s="2"/>
-      <c r="R959" s="2"/>
-      <c r="S959" s="2"/>
-      <c r="T959" s="2"/>
-      <c r="U959" s="2"/>
-      <c r="V959" s="2"/>
-      <c r="W959" s="2"/>
-      <c r="X959" s="2"/>
-      <c r="Y959" s="2"/>
-      <c r="Z959" s="2"/>
-      <c r="AA959" s="2"/>
-      <c r="AB959" s="2"/>
-    </row>
-    <row r="960" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A960" s="2"/>
-      <c r="B960" s="2"/>
-      <c r="C960" s="2"/>
-      <c r="D960" s="2"/>
-      <c r="E960" s="2"/>
-      <c r="F960" s="2"/>
-      <c r="G960" s="2"/>
-      <c r="H960" s="2"/>
-      <c r="I960" s="2"/>
-      <c r="J960" s="2"/>
-      <c r="K960" s="2"/>
-      <c r="L960" s="2"/>
-      <c r="M960" s="2"/>
-      <c r="N960" s="2"/>
-      <c r="O960" s="2"/>
-      <c r="P960" s="2"/>
-      <c r="Q960" s="2"/>
-      <c r="R960" s="2"/>
-      <c r="S960" s="2"/>
-      <c r="T960" s="2"/>
-      <c r="U960" s="2"/>
-      <c r="V960" s="2"/>
-      <c r="W960" s="2"/>
-      <c r="X960" s="2"/>
-      <c r="Y960" s="2"/>
-      <c r="Z960" s="2"/>
-      <c r="AA960" s="2"/>
-      <c r="AB960" s="2"/>
-    </row>
-    <row r="961" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A961" s="2"/>
-      <c r="B961" s="2"/>
-      <c r="C961" s="2"/>
-      <c r="D961" s="2"/>
-      <c r="E961" s="2"/>
-      <c r="F961" s="2"/>
-      <c r="G961" s="2"/>
-      <c r="H961" s="2"/>
-      <c r="I961" s="2"/>
-      <c r="J961" s="2"/>
-      <c r="K961" s="2"/>
-      <c r="L961" s="2"/>
-      <c r="M961" s="2"/>
-      <c r="N961" s="2"/>
-      <c r="O961" s="2"/>
-      <c r="P961" s="2"/>
-      <c r="Q961" s="2"/>
-      <c r="R961" s="2"/>
-      <c r="S961" s="2"/>
-      <c r="T961" s="2"/>
-      <c r="U961" s="2"/>
-      <c r="V961" s="2"/>
-      <c r="W961" s="2"/>
-      <c r="X961" s="2"/>
-      <c r="Y961" s="2"/>
-      <c r="Z961" s="2"/>
-      <c r="AA961" s="2"/>
-      <c r="AB961" s="2"/>
-    </row>
-    <row r="962" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A962" s="2"/>
-      <c r="B962" s="2"/>
-      <c r="C962" s="2"/>
-      <c r="D962" s="2"/>
-      <c r="E962" s="2"/>
-      <c r="F962" s="2"/>
-      <c r="G962" s="2"/>
-      <c r="H962" s="2"/>
-      <c r="I962" s="2"/>
-      <c r="J962" s="2"/>
-      <c r="K962" s="2"/>
-      <c r="L962" s="2"/>
-      <c r="M962" s="2"/>
-      <c r="N962" s="2"/>
-      <c r="O962" s="2"/>
-      <c r="P962" s="2"/>
-      <c r="Q962" s="2"/>
-      <c r="R962" s="2"/>
-      <c r="S962" s="2"/>
-      <c r="T962" s="2"/>
-      <c r="U962" s="2"/>
-      <c r="V962" s="2"/>
-      <c r="W962" s="2"/>
-      <c r="X962" s="2"/>
-      <c r="Y962" s="2"/>
-      <c r="Z962" s="2"/>
-      <c r="AA962" s="2"/>
-      <c r="AB962" s="2"/>
-    </row>
-    <row r="963" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A963" s="2"/>
-      <c r="B963" s="2"/>
-      <c r="C963" s="2"/>
-      <c r="D963" s="2"/>
-      <c r="E963" s="2"/>
-      <c r="F963" s="2"/>
-      <c r="G963" s="2"/>
-      <c r="H963" s="2"/>
-      <c r="I963" s="2"/>
-      <c r="J963" s="2"/>
-      <c r="K963" s="2"/>
-      <c r="L963" s="2"/>
-      <c r="M963" s="2"/>
-      <c r="N963" s="2"/>
-      <c r="O963" s="2"/>
-      <c r="P963" s="2"/>
-      <c r="Q963" s="2"/>
-      <c r="R963" s="2"/>
-      <c r="S963" s="2"/>
-      <c r="T963" s="2"/>
-      <c r="U963" s="2"/>
-      <c r="V963" s="2"/>
-      <c r="W963" s="2"/>
-      <c r="X963" s="2"/>
-      <c r="Y963" s="2"/>
-      <c r="Z963" s="2"/>
-      <c r="AA963" s="2"/>
-      <c r="AB963" s="2"/>
-    </row>
-    <row r="964" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A964" s="2"/>
-      <c r="B964" s="2"/>
-      <c r="C964" s="2"/>
-      <c r="D964" s="2"/>
-      <c r="E964" s="2"/>
-      <c r="F964" s="2"/>
-      <c r="G964" s="2"/>
-      <c r="H964" s="2"/>
-      <c r="I964" s="2"/>
-      <c r="J964" s="2"/>
-      <c r="K964" s="2"/>
-      <c r="L964" s="2"/>
-      <c r="M964" s="2"/>
-      <c r="N964" s="2"/>
-      <c r="O964" s="2"/>
-      <c r="P964" s="2"/>
-      <c r="Q964" s="2"/>
-      <c r="R964" s="2"/>
-      <c r="S964" s="2"/>
-      <c r="T964" s="2"/>
-      <c r="U964" s="2"/>
-      <c r="V964" s="2"/>
-      <c r="W964" s="2"/>
-      <c r="X964" s="2"/>
-      <c r="Y964" s="2"/>
-      <c r="Z964" s="2"/>
-      <c r="AA964" s="2"/>
-      <c r="AB964" s="2"/>
-    </row>
-    <row r="965" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A965" s="2"/>
-      <c r="B965" s="2"/>
-      <c r="C965" s="2"/>
-      <c r="D965" s="2"/>
-      <c r="E965" s="2"/>
-      <c r="F965" s="2"/>
-      <c r="G965" s="2"/>
-      <c r="H965" s="2"/>
-      <c r="I965" s="2"/>
-      <c r="J965" s="2"/>
-      <c r="K965" s="2"/>
-      <c r="L965" s="2"/>
-      <c r="M965" s="2"/>
-      <c r="N965" s="2"/>
-      <c r="O965" s="2"/>
-      <c r="P965" s="2"/>
-      <c r="Q965" s="2"/>
-      <c r="R965" s="2"/>
-      <c r="S965" s="2"/>
-      <c r="T965" s="2"/>
-      <c r="U965" s="2"/>
-      <c r="V965" s="2"/>
-      <c r="W965" s="2"/>
-      <c r="X965" s="2"/>
-      <c r="Y965" s="2"/>
-      <c r="Z965" s="2"/>
-      <c r="AA965" s="2"/>
-      <c r="AB965" s="2"/>
-    </row>
-    <row r="966" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A966" s="2"/>
-      <c r="B966" s="2"/>
-      <c r="C966" s="2"/>
-      <c r="D966" s="2"/>
-      <c r="E966" s="2"/>
-      <c r="F966" s="2"/>
-      <c r="G966" s="2"/>
-      <c r="H966" s="2"/>
-      <c r="I966" s="2"/>
-      <c r="J966" s="2"/>
-      <c r="K966" s="2"/>
-      <c r="L966" s="2"/>
-      <c r="M966" s="2"/>
-      <c r="N966" s="2"/>
-      <c r="O966" s="2"/>
-      <c r="P966" s="2"/>
-      <c r="Q966" s="2"/>
-      <c r="R966" s="2"/>
-      <c r="S966" s="2"/>
-      <c r="T966" s="2"/>
-      <c r="U966" s="2"/>
-      <c r="V966" s="2"/>
-      <c r="W966" s="2"/>
-      <c r="X966" s="2"/>
-      <c r="Y966" s="2"/>
-      <c r="Z966" s="2"/>
-      <c r="AA966" s="2"/>
-      <c r="AB966" s="2"/>
-    </row>
-    <row r="967" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A967" s="2"/>
-      <c r="B967" s="2"/>
-      <c r="C967" s="2"/>
-      <c r="D967" s="2"/>
-      <c r="E967" s="2"/>
-      <c r="F967" s="2"/>
-      <c r="G967" s="2"/>
-      <c r="H967" s="2"/>
-      <c r="I967" s="2"/>
-      <c r="J967" s="2"/>
-      <c r="K967" s="2"/>
-      <c r="L967" s="2"/>
-      <c r="M967" s="2"/>
-      <c r="N967" s="2"/>
-      <c r="O967" s="2"/>
-      <c r="P967" s="2"/>
-      <c r="Q967" s="2"/>
-      <c r="R967" s="2"/>
-      <c r="S967" s="2"/>
-      <c r="T967" s="2"/>
-      <c r="U967" s="2"/>
-      <c r="V967" s="2"/>
-      <c r="W967" s="2"/>
-      <c r="X967" s="2"/>
-      <c r="Y967" s="2"/>
-      <c r="Z967" s="2"/>
-      <c r="AA967" s="2"/>
-      <c r="AB967" s="2"/>
-    </row>
-    <row r="968" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A968" s="2"/>
-      <c r="B968" s="2"/>
-      <c r="C968" s="2"/>
-      <c r="D968" s="2"/>
-      <c r="E968" s="2"/>
-      <c r="F968" s="2"/>
-      <c r="G968" s="2"/>
-      <c r="H968" s="2"/>
-      <c r="I968" s="2"/>
-      <c r="J968" s="2"/>
-      <c r="K968" s="2"/>
-      <c r="L968" s="2"/>
-      <c r="M968" s="2"/>
-      <c r="N968" s="2"/>
-      <c r="O968" s="2"/>
-      <c r="P968" s="2"/>
-      <c r="Q968" s="2"/>
-      <c r="R968" s="2"/>
-      <c r="S968" s="2"/>
-      <c r="T968" s="2"/>
-      <c r="U968" s="2"/>
-      <c r="V968" s="2"/>
-      <c r="W968" s="2"/>
-      <c r="X968" s="2"/>
-      <c r="Y968" s="2"/>
-      <c r="Z968" s="2"/>
-      <c r="AA968" s="2"/>
-      <c r="AB968" s="2"/>
-    </row>
-    <row r="969" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A969" s="2"/>
-      <c r="B969" s="2"/>
-      <c r="C969" s="2"/>
-      <c r="D969" s="2"/>
-      <c r="E969" s="2"/>
-      <c r="F969" s="2"/>
-      <c r="G969" s="2"/>
-      <c r="H969" s="2"/>
-      <c r="I969" s="2"/>
-      <c r="J969" s="2"/>
-      <c r="K969" s="2"/>
-      <c r="L969" s="2"/>
-      <c r="M969" s="2"/>
-      <c r="N969" s="2"/>
-      <c r="O969" s="2"/>
-      <c r="P969" s="2"/>
-      <c r="Q969" s="2"/>
-      <c r="R969" s="2"/>
-      <c r="S969" s="2"/>
-      <c r="T969" s="2"/>
-      <c r="U969" s="2"/>
-      <c r="V969" s="2"/>
-      <c r="W969" s="2"/>
-      <c r="X969" s="2"/>
-      <c r="Y969" s="2"/>
-      <c r="Z969" s="2"/>
-      <c r="AA969" s="2"/>
-      <c r="AB969" s="2"/>
-    </row>
-    <row r="970" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A970" s="2"/>
-      <c r="B970" s="2"/>
-      <c r="C970" s="2"/>
-      <c r="D970" s="2"/>
-      <c r="E970" s="2"/>
-      <c r="F970" s="2"/>
-      <c r="G970" s="2"/>
-      <c r="H970" s="2"/>
-      <c r="I970" s="2"/>
-      <c r="J970" s="2"/>
-      <c r="K970" s="2"/>
-      <c r="L970" s="2"/>
-      <c r="M970" s="2"/>
-      <c r="N970" s="2"/>
-      <c r="O970" s="2"/>
-      <c r="P970" s="2"/>
-      <c r="Q970" s="2"/>
-      <c r="R970" s="2"/>
-      <c r="S970" s="2"/>
-      <c r="T970" s="2"/>
-      <c r="U970" s="2"/>
-      <c r="V970" s="2"/>
-      <c r="W970" s="2"/>
-      <c r="X970" s="2"/>
-      <c r="Y970" s="2"/>
-      <c r="Z970" s="2"/>
-      <c r="AA970" s="2"/>
-      <c r="AB970" s="2"/>
-    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="K4:K6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/nightwatch/ACTVN_TestCases.xlsx
+++ b/nightwatch/ACTVN_TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vien1\Downloads\OceanTech\School\kiemThuNhung\nightwatch-git\nightwatch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B5932C-18CB-4BAD-9A2A-EDDF8E56622C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B89C8E7-1C04-412C-8E30-4DF25A8DCF63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="210">
   <si>
     <t>ID</t>
   </si>
@@ -1053,6 +1053,15 @@
   </si>
   <si>
     <t>Xuất hiện alert với nội dung là "Vui lòng chọn tuổi lớn hơn 18", sau đó nhấn OK</t>
+  </si>
+  <si>
+    <t>Mở trình duyệt
+Truy cập trang "http://thuvienso.actvn.edu.vn"
+Chọn thẻ có id là "txtLoginUsername"
+Gõ "CT060146"
+Chọn thẻ có id là "txtLoginPassword"
+Gõ "CT060146"
+Bấm vào "Đăng nhập"</t>
   </si>
 </sst>
 </file>
@@ -1283,14 +1292,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1572,7 +1581,7 @@
         <v>135</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>136</v>
@@ -1639,10 +1648,10 @@
         <v>14</v>
       </c>
       <c r="I4" s="6"/>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="16" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1672,8 +1681,8 @@
         <v>14</v>
       </c>
       <c r="I5" s="9"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
@@ -2327,13 +2336,13 @@
       <c r="E28" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="15" t="s">
         <v>180</v>
       </c>
       <c r="G28" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="H28" s="17" t="s">
+      <c r="H28" s="15" t="s">
         <v>208</v>
       </c>
       <c r="I28" s="14"/>
@@ -2399,28 +2408,28 @@
       <c r="K30" s="2"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="15" t="s">
         <v>204</v>
       </c>
       <c r="D31" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="F31" s="17" t="s">
+      <c r="F31" s="15" t="s">
         <v>205</v>
       </c>
       <c r="G31" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H31" s="17" t="s">
+      <c r="H31" s="15" t="s">
         <v>14</v>
       </c>
       <c r="I31" s="14"/>
@@ -2428,7 +2437,7 @@
       <c r="K31" s="2"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="15" t="s">
         <v>206</v>
       </c>
       <c r="B32" s="14" t="s">
@@ -2440,16 +2449,16 @@
       <c r="D32" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="15" t="s">
         <v>199</v>
       </c>
       <c r="F32" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="G32" s="17" t="s">
+      <c r="G32" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="H32" s="17" t="s">
+      <c r="H32" s="15" t="s">
         <v>14</v>
       </c>
       <c r="I32" s="14"/>
@@ -2457,7 +2466,7 @@
       <c r="K32" s="2"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="15" t="s">
         <v>207</v>
       </c>
       <c r="B33" s="14" t="s">
@@ -2466,7 +2475,7 @@
       <c r="C33" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="15" t="s">
         <v>202</v>
       </c>
       <c r="E33" s="14" t="s">
